--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
+        <v>3</v>
+      </c>
+      <c r="G15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>2</v>
-      </c>
       <c r="H15" s="14">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="I15" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="15">
         <v>5</v>
       </c>
       <c r="K15" s="14">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="14">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>-40</v>
+        <v>-37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G16" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" s="14">
-        <v>-41.176470588235</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K16" s="14">
-        <v>-4.347826086956</v>
+        <v>18.518518518518</v>
       </c>
       <c r="L16" s="14">
-        <v>-38.888888888888</v>
+        <v>-20</v>
       </c>
       <c r="M16" s="14">
-        <v>-42.105263157894</v>
+        <v>-25.581395348837</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.871369294605</v>
+        <v>-88.965517241379</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D17" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E17" s="14">
-        <v>-62.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F17" s="15">
         <v>51</v>
       </c>
       <c r="G17" s="15">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="14">
-        <v>-1.923076923076</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="I17" s="15">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="J17" s="15">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="K17" s="14">
-        <v>-1.428571428571</v>
+        <v>-5.681818181818</v>
       </c>
       <c r="L17" s="14">
-        <v>6.153846153846</v>
+        <v>15.277777777777</v>
       </c>
       <c r="M17" s="14">
-        <v>46.808510638297</v>
+        <v>43.103448275862</v>
       </c>
       <c r="N17" s="14">
-        <v>-36.111111111111</v>
+        <v>-31.404958677686</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
+        <v>3</v>
+      </c>
+      <c r="D18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="15">
-        <v>3</v>
-      </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="F18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>33.333333333333</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I18" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="14">
-        <v>58.333333333333</v>
+        <v>76.923076923076</v>
       </c>
       <c r="L18" s="14">
-        <v>46.153846153846</v>
+        <v>64.285714285714</v>
       </c>
       <c r="M18" s="14">
-        <v>-32.142857142857</v>
+        <v>-37.837837837837</v>
       </c>
       <c r="N18" s="14">
-        <v>-73.239436619718</v>
+        <v>-72.941176470588</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>60</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" s="15">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H19" s="14">
-        <v>76.190476190476</v>
+        <v>80</v>
       </c>
       <c r="I19" s="15">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="J19" s="15">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K19" s="14">
-        <v>81.481481481481</v>
+        <v>69.696969696969</v>
       </c>
       <c r="L19" s="14">
-        <v>11.363636363636</v>
+        <v>7.692307692307</v>
       </c>
       <c r="M19" s="14">
-        <v>22.5</v>
+        <v>21.739130434782</v>
       </c>
       <c r="N19" s="14">
-        <v>-27.941176470588</v>
+        <v>-32.530120481927</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>200</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="15">
         <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J20" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K20" s="14">
-        <v>-25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L20" s="14">
-        <v>-59.090909090909</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M20" s="14">
-        <v>-25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N20" s="14">
-        <v>-86.764705882352</v>
+        <v>-88.636363636363</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.629629629629</v>
+        <v>12.903225806451</v>
       </c>
       <c r="F21" s="17">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H21" s="18">
-        <v>9.174311926605</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I21" s="17">
-        <v>171</v>
+        <v>209</v>
       </c>
       <c r="J21" s="17">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="K21" s="18">
-        <v>14.765100671140</v>
+        <v>16.111111111111</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.567567567567</v>
+        <v>0.480769230769</v>
       </c>
       <c r="M21" s="18">
-        <v>0</v>
+        <v>2.955665024630</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.894366197183</v>
+        <v>-69.354838709677</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>4</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-75</v>
       </c>
       <c r="F22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="14">
         <v>-50</v>
       </c>
       <c r="I22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" s="15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K22" s="14">
         <v>-75</v>
       </c>
       <c r="L22" s="14">
-        <v>-93.333333333333</v>
+        <v>-87.5</v>
       </c>
       <c r="M22" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>9</v>
       </c>
       <c r="D23" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>350</v>
       </c>
       <c r="F23" s="15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G23" s="15">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H23" s="14">
-        <v>-37.5</v>
+        <v>17.647058823529</v>
       </c>
       <c r="I23" s="15">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J23" s="15">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K23" s="14">
-        <v>-35.294117647058</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="L23" s="14">
-        <v>-46.341463414634</v>
+        <v>-35.416666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>-8.333333333333</v>
+        <v>19.230769230769</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14">
-        <v>57.894736842105</v>
+        <v>150</v>
       </c>
       <c r="F24" s="15">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="G24" s="15">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H24" s="14">
-        <v>72.058823529411</v>
+        <v>52.857142857142</v>
       </c>
       <c r="I24" s="15">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="J24" s="15">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K24" s="14">
-        <v>60</v>
+        <v>69.523809523809</v>
       </c>
       <c r="L24" s="14">
-        <v>18.75</v>
+        <v>13.375796178343</v>
       </c>
       <c r="M24" s="14">
-        <v>44.761904761904</v>
+        <v>50.847457627118</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="F25" s="15">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G25" s="15">
         <v>12</v>
       </c>
       <c r="H25" s="14">
-        <v>158.333333333333</v>
+        <v>191.666666666667</v>
       </c>
       <c r="I25" s="15">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J25" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="14">
-        <v>105.263157894737</v>
+        <v>150</v>
       </c>
       <c r="L25" s="14">
-        <v>8.333333333333</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D26" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E26" s="14">
-        <v>62.5</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F26" s="15">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="G26" s="15">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H26" s="14">
-        <v>31.746031746031</v>
+        <v>31.147540983606</v>
       </c>
       <c r="I26" s="15">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="J26" s="15">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="K26" s="14">
-        <v>25.581395348837</v>
+        <v>19.047619047619</v>
       </c>
       <c r="L26" s="14">
-        <v>38.461538461538</v>
+        <v>30.208333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>-14.960629921259</v>
+        <v>-17.763157894736</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
+        <v>3</v>
+      </c>
+      <c r="G27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
       <c r="H27" s="14">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
         <v>5</v>
       </c>
       <c r="K27" s="14">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G28" s="15">
         <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>83.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
         <v>14</v>
       </c>
       <c r="J28" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="14">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1488,19 +1488,19 @@
         <v>1</v>
       </c>
       <c r="J29" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="14">
         <v>-87.5</v>
       </c>
       <c r="M29" s="14">
-        <v>-80</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N29" s="14">
-        <v>-96</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1529,19 +1529,19 @@
         <v>1</v>
       </c>
       <c r="J30" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="14">
         <v>-85.714285714285</v>
       </c>
       <c r="M30" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="14">
-        <v>-96</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="15">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -881,8 +881,8 @@
       <c r="L14" s="14">
         <v>-100</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="14">
+        <v>-100</v>
       </c>
       <c r="N14" s="14">
         <v>-100</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>2</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>3</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>200</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
         <v>5</v>
@@ -923,10 +923,10 @@
         <v>66.666666666666</v>
       </c>
       <c r="M15" s="14">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N15" s="14">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D16" s="15">
         <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" s="15">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G16" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>26.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J16" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K16" s="14">
-        <v>18.518518518518</v>
+        <v>25.806451612903</v>
       </c>
       <c r="L16" s="14">
-        <v>-20</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>-25.581395348837</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="N16" s="14">
-        <v>-88.965517241379</v>
+        <v>-87.850467289719</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17" s="15">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E17" s="14">
-        <v>-22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="F17" s="15">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G17" s="15">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H17" s="14">
-        <v>-3.773584905660</v>
+        <v>-25</v>
       </c>
       <c r="I17" s="15">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J17" s="15">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="K17" s="14">
-        <v>-5.681818181818</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="L17" s="14">
-        <v>15.277777777777</v>
+        <v>14.634146341463</v>
       </c>
       <c r="M17" s="14">
-        <v>43.103448275862</v>
+        <v>36.231884057971</v>
       </c>
       <c r="N17" s="14">
-        <v>-31.404958677686</v>
+        <v>-31.386861313868</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F18" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>85.714285714285</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I18" s="15">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J18" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K18" s="14">
-        <v>76.923076923076</v>
+        <v>61.111111111111</v>
       </c>
       <c r="L18" s="14">
-        <v>64.285714285714</v>
+        <v>93.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-37.837837837837</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="N18" s="14">
-        <v>-72.941176470588</v>
+        <v>-72.115384615384</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>16.666666666666</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F19" s="15">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G19" s="15">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>80</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I19" s="15">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J19" s="15">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K19" s="14">
-        <v>69.696969696969</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L19" s="14">
-        <v>7.692307692307</v>
+        <v>1.694915254237</v>
       </c>
       <c r="M19" s="14">
-        <v>21.739130434782</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N19" s="14">
-        <v>-32.530120481927</v>
+        <v>-38.144329896907</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-50</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
         <v>6</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="14">
-        <v>-25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I20" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J20" s="15">
         <v>14</v>
       </c>
       <c r="K20" s="14">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L20" s="14">
-        <v>-58.333333333333</v>
+        <v>-52</v>
       </c>
       <c r="M20" s="14">
-        <v>-23.076923076923</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="14">
-        <v>-88.636363636363</v>
+        <v>-87.755102040816</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,63 +1139,63 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>12.903225806451</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="G21" s="17">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H21" s="18">
-        <v>19.047619047619</v>
+        <v>-1.801801801801</v>
       </c>
       <c r="I21" s="17">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="J21" s="17">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="K21" s="18">
-        <v>16.111111111111</v>
+        <v>13.809523809523</v>
       </c>
       <c r="L21" s="18">
-        <v>0.480769230769</v>
+        <v>3.017241379310</v>
       </c>
       <c r="M21" s="18">
-        <v>2.955665024630</v>
+        <v>1.702127659574</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.354838709677</v>
+        <v>-69.121447028423</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>1</v>
-      </c>
-      <c r="D22" s="15">
-        <v>4</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-75</v>
-      </c>
-      <c r="F22" s="15">
-        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>4</v>
       </c>
       <c r="H22" s="14">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
@@ -1207,10 +1207,10 @@
         <v>-75</v>
       </c>
       <c r="L22" s="14">
-        <v>-87.5</v>
+        <v>-88.235294117647</v>
       </c>
       <c r="M22" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E23" s="14">
-        <v>350</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F23" s="15">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G23" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H23" s="14">
-        <v>17.647058823529</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I23" s="15">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J23" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K23" s="14">
-        <v>-13.888888888888</v>
+        <v>-11.904761904761</v>
       </c>
       <c r="L23" s="14">
-        <v>-35.416666666666</v>
+        <v>-28.846153846153</v>
       </c>
       <c r="M23" s="14">
-        <v>19.230769230769</v>
+        <v>23.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D24" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="F24" s="15">
         <v>107</v>
       </c>
       <c r="G24" s="15">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H24" s="14">
-        <v>52.857142857142</v>
+        <v>62.121212121212</v>
       </c>
       <c r="I24" s="15">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="J24" s="15">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="K24" s="14">
-        <v>69.523809523809</v>
+        <v>65.6</v>
       </c>
       <c r="L24" s="14">
-        <v>13.375796178343</v>
+        <v>13.736263736263</v>
       </c>
       <c r="M24" s="14">
-        <v>50.847457627118</v>
+        <v>56.818181818181</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>11</v>
+      </c>
+      <c r="D25" s="15">
         <v>10</v>
       </c>
-      <c r="D25" s="15">
-        <v>1</v>
-      </c>
       <c r="E25" s="14">
-        <v>900</v>
+        <v>10</v>
       </c>
       <c r="F25" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G25" s="15">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H25" s="14">
-        <v>191.666666666667</v>
+        <v>123.529411764706</v>
       </c>
       <c r="I25" s="15">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="J25" s="15">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K25" s="14">
-        <v>150</v>
+        <v>103.333333333333</v>
       </c>
       <c r="L25" s="14">
-        <v>11.111111111111</v>
+        <v>15.094339622641</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" s="15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>-21.052631578947</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F26" s="15">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="G26" s="15">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H26" s="14">
-        <v>31.147540983606</v>
+        <v>12.698412698412</v>
       </c>
       <c r="I26" s="15">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="J26" s="15">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="K26" s="14">
-        <v>19.047619047619</v>
+        <v>19.491525423728</v>
       </c>
       <c r="L26" s="14">
-        <v>30.208333333333</v>
+        <v>34.285714285714</v>
       </c>
       <c r="M26" s="14">
-        <v>-17.763157894736</v>
+        <v>-15.060240963855</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
-        <v>3</v>
-      </c>
-      <c r="G27" s="15">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14">
-        <v>200</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
         <v>50</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="15">
         <v>12</v>
       </c>
       <c r="K28" s="14">
-        <v>16.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L28" s="14">
-        <v>75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,14 +1466,14 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="15">
+      <c r="C29" s="15">
         <v>1</v>
       </c>
-      <c r="E29" s="14">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="15">
         <v>1</v>
@@ -1485,36 +1485,36 @@
         <v>-50</v>
       </c>
       <c r="I29" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="15">
         <v>3</v>
       </c>
       <c r="K29" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="14">
-        <v>-87.5</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M29" s="14">
-        <v>-85.714285714285</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="14">
-        <v>-96.153846153846</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="15">
+      <c r="C30" s="15">
         <v>1</v>
       </c>
-      <c r="E30" s="14">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="15">
         <v>1</v>
@@ -1526,22 +1526,22 @@
         <v>-50</v>
       </c>
       <c r="I30" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="15">
         <v>3</v>
       </c>
       <c r="K30" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L30" s="14">
+        <v>-75</v>
+      </c>
+      <c r="M30" s="14">
         <v>-66.666666666666</v>
       </c>
-      <c r="L30" s="14">
-        <v>-85.714285714285</v>
-      </c>
-      <c r="M30" s="14">
-        <v>-80</v>
-      </c>
       <c r="N30" s="14">
-        <v>-96.153846153846</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,22 +878,22 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="M14" s="14">
-        <v>-100</v>
-      </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>-75</v>
+      </c>
+      <c r="M14" s="15">
+        <v>0</v>
+      </c>
+      <c r="N14" s="15">
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
-        <v>2</v>
+      <c r="F15" s="14">
+        <v>4</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -910,228 +910,228 @@
       <c r="H15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
+        <v>7</v>
+      </c>
+      <c r="J15" s="14">
         <v>5</v>
       </c>
-      <c r="J15" s="15">
-        <v>5</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0</v>
-      </c>
-      <c r="L15" s="14">
-        <v>66.666666666666</v>
-      </c>
-      <c r="M15" s="14">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="N15" s="14">
-        <v>-44.444444444444</v>
+      <c r="K15" s="15">
+        <v>40</v>
+      </c>
+      <c r="L15" s="15">
+        <v>75</v>
+      </c>
+      <c r="M15" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="N15" s="15">
+        <v>-46.153846153846</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>6</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="14">
         <v>4</v>
       </c>
-      <c r="E16" s="14">
-        <v>50</v>
-      </c>
-      <c r="F16" s="15">
-        <v>19</v>
-      </c>
-      <c r="G16" s="15">
-        <v>15</v>
-      </c>
-      <c r="H16" s="14">
-        <v>26.666666666666</v>
-      </c>
-      <c r="I16" s="15">
-        <v>39</v>
-      </c>
-      <c r="J16" s="15">
-        <v>31</v>
-      </c>
-      <c r="K16" s="14">
-        <v>25.806451612903</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-13.333333333333</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-20.408163265306</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-87.850467289719</v>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>22</v>
+      </c>
+      <c r="G16" s="14">
+        <v>14</v>
+      </c>
+      <c r="H16" s="15">
+        <v>57.142857142857</v>
+      </c>
+      <c r="I16" s="14">
+        <v>43</v>
+      </c>
+      <c r="J16" s="14">
+        <v>35</v>
+      </c>
+      <c r="K16" s="15">
+        <v>22.857142857142</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-15.686274509803</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-25.862068965517</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-88.315217391304</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>11</v>
-      </c>
-      <c r="D17" s="15">
-        <v>10</v>
-      </c>
-      <c r="E17" s="14">
-        <v>10</v>
-      </c>
-      <c r="F17" s="15">
-        <v>39</v>
-      </c>
-      <c r="G17" s="15">
-        <v>52</v>
-      </c>
-      <c r="H17" s="14">
+      <c r="C17" s="14">
+        <v>17</v>
+      </c>
+      <c r="D17" s="14">
+        <v>20</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-15</v>
+      </c>
+      <c r="F17" s="14">
+        <v>48</v>
+      </c>
+      <c r="G17" s="14">
+        <v>64</v>
+      </c>
+      <c r="H17" s="15">
         <v>-25</v>
       </c>
-      <c r="I17" s="15">
-        <v>94</v>
-      </c>
-      <c r="J17" s="15">
-        <v>98</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-4.081632653061</v>
-      </c>
-      <c r="L17" s="14">
-        <v>14.634146341463</v>
-      </c>
-      <c r="M17" s="14">
-        <v>36.231884057971</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-31.386861313868</v>
+      <c r="I17" s="14">
+        <v>111</v>
+      </c>
+      <c r="J17" s="14">
+        <v>118</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-5.932203389830</v>
+      </c>
+      <c r="L17" s="15">
+        <v>13.265306122449</v>
+      </c>
+      <c r="M17" s="15">
+        <v>50</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-27.450980392156</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>5</v>
       </c>
-      <c r="D18" s="15">
-        <v>5</v>
-      </c>
-      <c r="E18" s="14">
+      <c r="E18" s="15">
+        <v>-40</v>
+      </c>
+      <c r="F18" s="14">
+        <v>14</v>
+      </c>
+      <c r="G18" s="14">
+        <v>14</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="15">
-        <v>15</v>
-      </c>
-      <c r="G18" s="15">
-        <v>11</v>
-      </c>
-      <c r="H18" s="14">
-        <v>36.363636363636</v>
-      </c>
-      <c r="I18" s="15">
-        <v>29</v>
-      </c>
-      <c r="J18" s="15">
-        <v>18</v>
-      </c>
-      <c r="K18" s="14">
-        <v>61.111111111111</v>
-      </c>
-      <c r="L18" s="14">
-        <v>93.333333333333</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-25.641025641025</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-72.115384615384</v>
+      <c r="I18" s="14">
+        <v>32</v>
+      </c>
+      <c r="J18" s="14">
+        <v>23</v>
+      </c>
+      <c r="K18" s="15">
+        <v>39.130434782608</v>
+      </c>
+      <c r="L18" s="15">
+        <v>77.777777777777</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-23.809523809523</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-74.193548387096</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>5</v>
-      </c>
-      <c r="D19" s="15">
-        <v>11</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-54.545454545454</v>
-      </c>
-      <c r="F19" s="15">
-        <v>28</v>
-      </c>
-      <c r="G19" s="15">
-        <v>26</v>
-      </c>
-      <c r="H19" s="14">
-        <v>7.692307692307</v>
-      </c>
-      <c r="I19" s="15">
-        <v>60</v>
-      </c>
-      <c r="J19" s="15">
-        <v>44</v>
-      </c>
-      <c r="K19" s="14">
-        <v>36.363636363636</v>
-      </c>
-      <c r="L19" s="14">
-        <v>1.694915254237</v>
-      </c>
-      <c r="M19" s="14">
-        <v>11.111111111111</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-38.144329896907</v>
+      <c r="C19" s="14">
+        <v>2</v>
+      </c>
+      <c r="D19" s="14">
+        <v>13</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-84.615384615384</v>
+      </c>
+      <c r="F19" s="14">
+        <v>21</v>
+      </c>
+      <c r="G19" s="14">
+        <v>35</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-40</v>
+      </c>
+      <c r="I19" s="14">
+        <v>61</v>
+      </c>
+      <c r="J19" s="14">
+        <v>57</v>
+      </c>
+      <c r="K19" s="15">
+        <v>7.017543859649</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-8.955223880597</v>
+      </c>
+      <c r="M19" s="15">
+        <v>7.017543859649</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-44.545454545454</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="14">
         <v>6</v>
       </c>
-      <c r="G20" s="15">
-        <v>7</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="I20" s="15">
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0</v>
+      </c>
+      <c r="I20" s="14">
         <v>12</v>
       </c>
-      <c r="J20" s="15">
-        <v>14</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-14.285714285714</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-52</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-25</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-87.755102040816</v>
+      <c r="J20" s="14">
+        <v>17</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-29.411764705882</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-58.620689655172</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-36.842105263157</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-88.785046728972</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E21" s="18">
-        <v>-6.666666666666</v>
+        <v>-37.777777777777</v>
       </c>
       <c r="F21" s="17">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G21" s="17">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.801801801801</v>
+        <v>-12.781954887218</v>
       </c>
       <c r="I21" s="17">
-        <v>239</v>
+        <v>267</v>
       </c>
       <c r="J21" s="17">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="K21" s="18">
-        <v>13.809523809523</v>
+        <v>4.705882352941</v>
       </c>
       <c r="L21" s="18">
-        <v>3.017241379310</v>
+        <v>-1.476014760147</v>
       </c>
       <c r="M21" s="18">
-        <v>1.702127659574</v>
+        <v>3.088803088803</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.121447028423</v>
+        <v>-69.796380090497</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>4</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-75</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-80</v>
+      </c>
+      <c r="I22" s="14">
         <v>2</v>
       </c>
-      <c r="J22" s="15">
-        <v>8</v>
-      </c>
-      <c r="K22" s="14">
-        <v>-75</v>
-      </c>
-      <c r="L22" s="14">
-        <v>-88.235294117647</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-66.666666666666</v>
+      <c r="J22" s="14">
+        <v>9</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-77.777777777777</v>
+      </c>
+      <c r="L22" s="15">
+        <v>-90</v>
+      </c>
+      <c r="M22" s="15">
+        <v>-71.428571428571</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>5</v>
-      </c>
-      <c r="D23" s="15">
-        <v>6</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="F23" s="15">
-        <v>19</v>
-      </c>
-      <c r="G23" s="15">
-        <v>18</v>
-      </c>
-      <c r="H23" s="14">
-        <v>5.555555555555</v>
-      </c>
-      <c r="I23" s="15">
-        <v>37</v>
-      </c>
-      <c r="J23" s="15">
-        <v>42</v>
-      </c>
-      <c r="K23" s="14">
-        <v>-11.904761904761</v>
-      </c>
-      <c r="L23" s="14">
-        <v>-28.846153846153</v>
-      </c>
-      <c r="M23" s="14">
-        <v>23.333333333333</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>9</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-77.777777777777</v>
+      </c>
+      <c r="F23" s="14">
+        <v>16</v>
+      </c>
+      <c r="G23" s="14">
+        <v>22</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-27.272727272727</v>
+      </c>
+      <c r="I23" s="14">
+        <v>38</v>
+      </c>
+      <c r="J23" s="14">
+        <v>51</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-25.490196078431</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-37.704918032786</v>
+      </c>
+      <c r="M23" s="15">
+        <v>18.75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>31</v>
-      </c>
-      <c r="D24" s="15">
-        <v>20</v>
-      </c>
-      <c r="E24" s="14">
-        <v>55</v>
-      </c>
-      <c r="F24" s="15">
-        <v>107</v>
-      </c>
-      <c r="G24" s="15">
-        <v>66</v>
-      </c>
-      <c r="H24" s="14">
-        <v>62.121212121212</v>
-      </c>
-      <c r="I24" s="15">
-        <v>207</v>
-      </c>
-      <c r="J24" s="15">
-        <v>125</v>
-      </c>
-      <c r="K24" s="14">
-        <v>65.6</v>
-      </c>
-      <c r="L24" s="14">
-        <v>13.736263736263</v>
-      </c>
-      <c r="M24" s="14">
-        <v>56.818181818181</v>
+      <c r="C24" s="14">
+        <v>17</v>
+      </c>
+      <c r="D24" s="14">
+        <v>20</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-15</v>
+      </c>
+      <c r="F24" s="14">
+        <v>105</v>
+      </c>
+      <c r="G24" s="14">
+        <v>69</v>
+      </c>
+      <c r="H24" s="15">
+        <v>52.173913043478</v>
+      </c>
+      <c r="I24" s="14">
+        <v>226</v>
+      </c>
+      <c r="J24" s="14">
+        <v>145</v>
+      </c>
+      <c r="K24" s="15">
+        <v>55.862068965517</v>
+      </c>
+      <c r="L24" s="15">
+        <v>8.133971291866</v>
+      </c>
+      <c r="M24" s="15">
+        <v>56.944444444444</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>11</v>
-      </c>
-      <c r="D25" s="15">
-        <v>10</v>
-      </c>
-      <c r="E25" s="14">
-        <v>10</v>
-      </c>
-      <c r="F25" s="15">
-        <v>38</v>
-      </c>
-      <c r="G25" s="15">
-        <v>17</v>
-      </c>
-      <c r="H25" s="14">
-        <v>123.529411764706</v>
-      </c>
-      <c r="I25" s="15">
-        <v>61</v>
-      </c>
-      <c r="J25" s="15">
-        <v>30</v>
-      </c>
-      <c r="K25" s="14">
-        <v>103.333333333333</v>
-      </c>
-      <c r="L25" s="14">
-        <v>15.094339622641</v>
+      <c r="C25" s="14">
+        <v>6</v>
+      </c>
+      <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <v>100</v>
+      </c>
+      <c r="F25" s="14">
+        <v>35</v>
+      </c>
+      <c r="G25" s="14">
+        <v>19</v>
+      </c>
+      <c r="H25" s="15">
+        <v>84.210526315789</v>
+      </c>
+      <c r="I25" s="14">
+        <v>67</v>
+      </c>
+      <c r="J25" s="14">
+        <v>33</v>
+      </c>
+      <c r="K25" s="15">
+        <v>103.030303030303</v>
+      </c>
+      <c r="L25" s="15">
+        <v>9.836065573770</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>16</v>
-      </c>
-      <c r="D26" s="15">
-        <v>13</v>
-      </c>
-      <c r="E26" s="14">
-        <v>23.076923076923</v>
-      </c>
-      <c r="F26" s="15">
-        <v>71</v>
-      </c>
-      <c r="G26" s="15">
-        <v>63</v>
-      </c>
-      <c r="H26" s="14">
-        <v>12.698412698412</v>
-      </c>
-      <c r="I26" s="15">
-        <v>141</v>
-      </c>
-      <c r="J26" s="15">
-        <v>118</v>
-      </c>
-      <c r="K26" s="14">
-        <v>19.491525423728</v>
-      </c>
-      <c r="L26" s="14">
-        <v>34.285714285714</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-15.060240963855</v>
+      <c r="C26" s="14">
+        <v>11</v>
+      </c>
+      <c r="D26" s="14">
+        <v>12</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-8.333333333333</v>
+      </c>
+      <c r="F26" s="14">
+        <v>70</v>
+      </c>
+      <c r="G26" s="14">
+        <v>60</v>
+      </c>
+      <c r="H26" s="15">
+        <v>16.666666666666</v>
+      </c>
+      <c r="I26" s="14">
+        <v>152</v>
+      </c>
+      <c r="J26" s="14">
+        <v>130</v>
+      </c>
+      <c r="K26" s="15">
+        <v>16.923076923076</v>
+      </c>
+      <c r="L26" s="15">
+        <v>21.6</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-16.939890710382</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
-        <v>2</v>
+      <c r="F27" s="14">
+        <v>4</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1402,17 +1402,17 @@
       <c r="H27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
+        <v>7</v>
+      </c>
+      <c r="J27" s="14">
         <v>5</v>
       </c>
-      <c r="J27" s="15">
-        <v>5</v>
-      </c>
-      <c r="K27" s="14">
-        <v>0</v>
-      </c>
-      <c r="L27" s="14">
-        <v>0</v>
+      <c r="K27" s="15">
+        <v>40</v>
+      </c>
+      <c r="L27" s="15">
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>6</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
         <v>4</v>
       </c>
-      <c r="H28" s="14">
-        <v>50</v>
-      </c>
-      <c r="I28" s="15">
-        <v>15</v>
-      </c>
-      <c r="J28" s="15">
-        <v>12</v>
-      </c>
-      <c r="K28" s="14">
-        <v>25</v>
-      </c>
-      <c r="L28" s="14">
-        <v>66.666666666666</v>
+      <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0</v>
+      </c>
+      <c r="I28" s="14">
+        <v>17</v>
+      </c>
+      <c r="J28" s="14">
+        <v>14</v>
+      </c>
+      <c r="K28" s="15">
+        <v>21.428571428571</v>
+      </c>
+      <c r="L28" s="15">
+        <v>54.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="15">
+      <c r="E29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I29" s="14">
         <v>2</v>
       </c>
-      <c r="H29" s="14">
+      <c r="J29" s="14">
+        <v>4</v>
+      </c>
+      <c r="K29" s="15">
         <v>-50</v>
       </c>
-      <c r="I29" s="15">
-        <v>2</v>
-      </c>
-      <c r="J29" s="15">
-        <v>3</v>
-      </c>
-      <c r="K29" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L29" s="14">
-        <v>-77.777777777777</v>
-      </c>
-      <c r="M29" s="14">
+      <c r="L29" s="15">
+        <v>-80</v>
+      </c>
+      <c r="M29" s="15">
         <v>-75</v>
       </c>
-      <c r="N29" s="14">
-        <v>-93.75</v>
+      <c r="N29" s="15">
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="15">
+      <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="15">
+      <c r="G30" s="14">
+        <v>3</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I30" s="14">
         <v>2</v>
       </c>
-      <c r="H30" s="14">
+      <c r="J30" s="14">
+        <v>4</v>
+      </c>
+      <c r="K30" s="15">
         <v>-50</v>
       </c>
-      <c r="I30" s="15">
-        <v>2</v>
-      </c>
-      <c r="J30" s="15">
-        <v>3</v>
-      </c>
-      <c r="K30" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L30" s="14">
-        <v>-75</v>
-      </c>
-      <c r="M30" s="14">
+      <c r="L30" s="15">
+        <v>-77.777777777777</v>
+      </c>
+      <c r="M30" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="N30" s="14">
-        <v>-93.75</v>
+      <c r="N30" s="15">
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1566,7 +1566,7 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="14">
         <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
@@ -1625,7 +1625,7 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="14">
         <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>60</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>74</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>26</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>26</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>7</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>-73.076923076923</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-73.076923076923</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-90.540540540540</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-88.333333333333</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>113</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>88</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>74</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>54</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>44</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>-18.518518518518</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-40.540540540540</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-50</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-61.061946902654</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>2914</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>2252</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>879</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>625</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>304</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-51.36</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-65.415244596132</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-86.500888099467</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-89.567604667124</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>1519</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>1143</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>816</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>665</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>843</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>26.766917293233</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>3.308823529411</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-26.246719160105</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-44.502962475312</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1313</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>789</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>501</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>522</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>209</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-59.961685823754</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-58.283433133732</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-73.510773130545</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-84.082254379284</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>1293</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>949</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>418</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>409</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>494</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>20.782396088019</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>18.181818181818</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-47.945205479452</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-61.794276875483</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>1031</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>713</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>309</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>296</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>138</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-53.378378378378</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-55.339805825242</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-80.645161290322</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-86.614936954413</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,32 +851,32 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>0</v>
       </c>
       <c r="L14" s="15">
         <v>-75</v>
@@ -890,221 +890,221 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>500</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="M15" s="15">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-46.153846153846</v>
+        <v>-47.058823529411</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>57.142857142857</v>
+        <v>80</v>
       </c>
       <c r="I16" s="14">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>22.857142857142</v>
+        <v>34.210526315789</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.686274509803</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="M16" s="15">
-        <v>-25.862068965517</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.315217391304</v>
+        <v>-87.857142857142</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
+        <v>12</v>
+      </c>
+      <c r="D17" s="14">
         <v>17</v>
       </c>
-      <c r="D17" s="14">
-        <v>20</v>
-      </c>
       <c r="E17" s="15">
-        <v>-15</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F17" s="14">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H17" s="15">
-        <v>-25</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="I17" s="14">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J17" s="14">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.932203389830</v>
+        <v>-8.148148148148</v>
       </c>
       <c r="L17" s="15">
-        <v>13.265306122449</v>
+        <v>14.814814814814</v>
       </c>
       <c r="M17" s="15">
-        <v>50</v>
+        <v>37.777777777777</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.450980392156</v>
+        <v>-29.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
         <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J18" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K18" s="15">
-        <v>39.130434782608</v>
+        <v>48</v>
       </c>
       <c r="L18" s="15">
-        <v>77.777777777777</v>
+        <v>68.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.809523809523</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.193548387096</v>
+        <v>-73.943661971831</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-84.615384615384</v>
+        <v>-62.5</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-40</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I19" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J19" s="14">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="K19" s="15">
-        <v>7.017543859649</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>-8.955223880597</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M19" s="15">
-        <v>7.017543859649</v>
+        <v>4.838709677419</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.545454545454</v>
+        <v>-48.818897637795</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
         <v>6</v>
@@ -1116,77 +1116,77 @@
         <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>-29.411764705882</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-58.620689655172</v>
+        <v>-53.125</v>
       </c>
       <c r="M20" s="15">
-        <v>-36.842105263157</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.785046728972</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.777777777777</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="F21" s="17">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G21" s="17">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.781954887218</v>
+        <v>-8.633093525179</v>
       </c>
       <c r="I21" s="17">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="J21" s="17">
-        <v>255</v>
+        <v>288</v>
       </c>
       <c r="K21" s="18">
-        <v>4.705882352941</v>
+        <v>4.861111111111</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.476014760147</v>
+        <v>2.372881355932</v>
       </c>
       <c r="M21" s="18">
-        <v>3.088803088803</v>
+        <v>2.372881355932</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.796380090497</v>
+        <v>-70.099009900990</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1207,13 +1207,13 @@
         <v>-77.777777777777</v>
       </c>
       <c r="L22" s="15">
-        <v>-90</v>
+        <v>-90.476190476190</v>
       </c>
       <c r="M22" s="15">
-        <v>-71.428571428571</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-77.777777777777</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G23" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H23" s="15">
-        <v>-27.272727272727</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I23" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J23" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K23" s="15">
-        <v>-25.490196078431</v>
+        <v>-24.561403508771</v>
       </c>
       <c r="L23" s="15">
-        <v>-37.704918032786</v>
+        <v>-33.846153846153</v>
       </c>
       <c r="M23" s="15">
-        <v>18.75</v>
+        <v>16.216216216216</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
         <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>-15</v>
+        <v>55</v>
       </c>
       <c r="F24" s="14">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G24" s="14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H24" s="15">
-        <v>52.173913043478</v>
+        <v>51.428571428571</v>
       </c>
       <c r="I24" s="14">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="J24" s="14">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="K24" s="15">
-        <v>55.862068965517</v>
+        <v>56.363636363636</v>
       </c>
       <c r="L24" s="15">
-        <v>8.133971291866</v>
+        <v>12.663755458515</v>
       </c>
       <c r="M24" s="15">
-        <v>56.944444444444</v>
+        <v>52.662721893491</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1306,37 +1306,37 @@
         <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G25" s="14">
         <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>84.210526315789</v>
+        <v>73.684210526315</v>
       </c>
       <c r="I25" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J25" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K25" s="15">
-        <v>103.030303030303</v>
+        <v>92.105263157894</v>
       </c>
       <c r="L25" s="15">
-        <v>9.836065573770</v>
+        <v>7.352941176470</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E26" s="15">
-        <v>-8.333333333333</v>
+        <v>-28</v>
       </c>
       <c r="F26" s="14">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G26" s="14">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H26" s="15">
-        <v>16.666666666666</v>
+        <v>-7.246376811594</v>
       </c>
       <c r="I26" s="14">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="J26" s="14">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="K26" s="15">
-        <v>16.923076923076</v>
+        <v>11.612903225806</v>
       </c>
       <c r="L26" s="15">
-        <v>21.6</v>
+        <v>21.830985915493</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.939890710382</v>
+        <v>-19.158878504672</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>500</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1428,38 +1428,38 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>21.428571428571</v>
+        <v>35.714285714285</v>
       </c>
       <c r="L28" s="15">
-        <v>54.545454545454</v>
+        <v>58.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1479,28 +1479,28 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.444444444444</v>
+        <v>-94.871794871794</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1511,7 +1511,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="15">
         <v>-100</v>
@@ -1520,28 +1520,28 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="M30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.444444444444</v>
+        <v>-94.871794871794</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>113</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>2914</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1519</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1313</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>1293</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>1031</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>8243</v>

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -879,223 +879,223 @@
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M14" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="14">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
         <v>100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>6</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>500</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L15" s="15">
         <v>125</v>
       </c>
       <c r="M15" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-47.058823529411</v>
+        <v>-59.090909090909</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
         <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>80</v>
+        <v>84.615384615384</v>
       </c>
       <c r="I16" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J16" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>34.210526315789</v>
+        <v>42.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.272727272727</v>
+        <v>-5</v>
       </c>
       <c r="M16" s="15">
-        <v>-22.727272727272</v>
+        <v>-21.917808219178</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.857142857142</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-29.411764705882</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F17" s="14">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G17" s="14">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.923076923076</v>
+        <v>-5.357142857142</v>
       </c>
       <c r="I17" s="14">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="J17" s="14">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.148148148148</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L17" s="15">
-        <v>14.814814814814</v>
+        <v>7.936507936507</v>
       </c>
       <c r="M17" s="15">
-        <v>37.777777777777</v>
+        <v>34.653465346534</v>
       </c>
       <c r="N17" s="15">
-        <v>-29.142857142857</v>
+        <v>-28.421052631578</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>30.769230769230</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>48</v>
+        <v>44.827586206896</v>
       </c>
       <c r="L18" s="15">
-        <v>68.181818181818</v>
+        <v>75</v>
       </c>
       <c r="M18" s="15">
-        <v>-21.276595744680</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-73.943661971831</v>
+        <v>-73.584905660377</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>8</v>
+      </c>
+      <c r="D19" s="14">
         <v>3</v>
       </c>
-      <c r="D19" s="14">
-        <v>8</v>
-      </c>
       <c r="E19" s="15">
-        <v>-62.5</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F19" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>-57.894736842105</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J19" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.142857142857</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="M19" s="15">
-        <v>4.838709677419</v>
+        <v>8.823529411764</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.818897637795</v>
+        <v>-45.985401459854</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
         <v>3</v>
@@ -1107,77 +1107,77 @@
         <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I20" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.666666666666</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L20" s="15">
-        <v>-53.125</v>
+        <v>-48.571428571428</v>
       </c>
       <c r="M20" s="15">
-        <v>-28.571428571428</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.5</v>
+        <v>-86.153846153846</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.121212121212</v>
+        <v>60</v>
       </c>
       <c r="F21" s="17">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G21" s="17">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.633093525179</v>
+        <v>-1.5625</v>
       </c>
       <c r="I21" s="17">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="J21" s="17">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="K21" s="18">
-        <v>4.861111111111</v>
+        <v>9.415584415584</v>
       </c>
       <c r="L21" s="18">
-        <v>2.372881355932</v>
+        <v>1.506024096385</v>
       </c>
       <c r="M21" s="18">
-        <v>2.372881355932</v>
+        <v>2.121212121212</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.099009900990</v>
+        <v>-69.474637681159</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1186,16 +1186,16 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="14">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="14">
-        <v>5</v>
-      </c>
       <c r="H22" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
@@ -1210,10 +1210,10 @@
         <v>-90.476190476190</v>
       </c>
       <c r="M22" s="15">
-        <v>-77.777777777777</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>7</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="14">
-        <v>6</v>
-      </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="15">
-        <v>-13.043478260869</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J23" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K23" s="15">
-        <v>-24.561403508771</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>-33.846153846153</v>
+        <v>-35.897435897435</v>
       </c>
       <c r="M23" s="15">
-        <v>16.216216216216</v>
+        <v>25</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
         <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G24" s="14">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H24" s="15">
-        <v>51.428571428571</v>
+        <v>27.5</v>
       </c>
       <c r="I24" s="14">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="J24" s="14">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="K24" s="15">
-        <v>56.363636363636</v>
+        <v>49.729729729729</v>
       </c>
       <c r="L24" s="15">
-        <v>12.663755458515</v>
+        <v>7.782101167315</v>
       </c>
       <c r="M24" s="15">
-        <v>52.662721893491</v>
+        <v>47.340425531914</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>73.684210526315</v>
+        <v>70</v>
       </c>
       <c r="I25" s="14">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="J25" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K25" s="15">
-        <v>92.105263157894</v>
+        <v>110</v>
       </c>
       <c r="L25" s="15">
-        <v>7.352941176470</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,81 +1344,81 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>-28</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="F26" s="14">
         <v>64</v>
       </c>
       <c r="G26" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H26" s="15">
-        <v>-7.246376811594</v>
+        <v>-12.328767123287</v>
       </c>
       <c r="I26" s="14">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="J26" s="14">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="K26" s="15">
-        <v>11.612903225806</v>
+        <v>5.617977528089</v>
       </c>
       <c r="L26" s="15">
-        <v>21.830985915493</v>
+        <v>16.770186335403</v>
       </c>
       <c r="M26" s="15">
-        <v>-19.158878504672</v>
+        <v>-23.577235772357</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
         <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>6</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>500</v>
       </c>
       <c r="I27" s="14">
         <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L27" s="15">
         <v>12.5</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>6</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" s="14">
-        <v>5</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
-      </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
         <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>35.714285714285</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L28" s="15">
-        <v>58.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
@@ -1494,13 +1494,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-81.818181818181</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M29" s="15">
         <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.871794871794</v>
+        <v>-95.744680851063</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
@@ -1535,13 +1535,13 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="M30" s="15">
         <v>-75</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.871794871794</v>
+        <v>-95.555555555555</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>113</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>2914</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1519</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>1313</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>1293</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>1031</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>8243</v>

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -885,21 +885,21 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-90</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>4</v>
@@ -911,22 +911,22 @@
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="M15" s="15">
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-59.090909090909</v>
+        <v>-56.521739130434</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>84.615384615384</v>
+        <v>81.818181818181</v>
       </c>
       <c r="I16" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K16" s="15">
-        <v>42.5</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L16" s="15">
-        <v>-5</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.917808219178</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.5</v>
+        <v>-88.304093567251</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>15</v>
+      </c>
+      <c r="D17" s="14">
         <v>10</v>
       </c>
-      <c r="D17" s="14">
-        <v>9</v>
-      </c>
       <c r="E17" s="15">
-        <v>11.111111111111</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G17" s="14">
         <v>56</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.357142857142</v>
+        <v>1.785714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="J17" s="14">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.555555555555</v>
+        <v>-1.298701298701</v>
       </c>
       <c r="L17" s="15">
-        <v>7.936507936507</v>
+        <v>9.352517985611</v>
       </c>
       <c r="M17" s="15">
-        <v>34.653465346534</v>
+        <v>29.914529914529</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.421052631578</v>
+        <v>-27.619047619047</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
-      </c>
-      <c r="D18" s="14">
-        <v>4</v>
-      </c>
-      <c r="E18" s="15">
-        <v>25</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>12.5</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I18" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
         <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>44.827586206896</v>
+        <v>55.172413793103</v>
       </c>
       <c r="L18" s="15">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.222222222222</v>
+        <v>-23.728813559322</v>
       </c>
       <c r="N18" s="15">
-        <v>-73.584905660377</v>
+        <v>-74.431818181818</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E19" s="15">
-        <v>166.666666666667</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>-45.714285714285</v>
+        <v>-37.5</v>
       </c>
       <c r="I19" s="14">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J19" s="14">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="K19" s="15">
-        <v>8.823529411764</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.128205128205</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M19" s="15">
-        <v>8.823529411764</v>
+        <v>12</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.985401459854</v>
+        <v>-42.465753424657</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K20" s="15">
-        <v>-5.263157894736</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L20" s="15">
-        <v>-48.571428571428</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="M20" s="15">
-        <v>-18.181818181818</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.153846153846</v>
+        <v>-85.185185185185</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E21" s="18">
-        <v>60</v>
+        <v>6.451612903225</v>
       </c>
       <c r="F21" s="17">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G21" s="17">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.5625</v>
+        <v>1.550387596899</v>
       </c>
       <c r="I21" s="17">
-        <v>337</v>
+        <v>372</v>
       </c>
       <c r="J21" s="17">
-        <v>308</v>
+        <v>339</v>
       </c>
       <c r="K21" s="18">
-        <v>9.415584415584</v>
+        <v>9.734513274336</v>
       </c>
       <c r="L21" s="18">
-        <v>1.506024096385</v>
+        <v>2.762430939226</v>
       </c>
       <c r="M21" s="18">
-        <v>2.121212121212</v>
+        <v>-0.534759358288</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.474637681159</v>
+        <v>-69.382716049382</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,17 +1182,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,16 +1201,16 @@
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>-77.777777777777</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="L22" s="15">
-        <v>-90.476190476190</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="M22" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>133.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F23" s="14">
         <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J23" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K23" s="15">
-        <v>-16.666666666666</v>
+        <v>-12.698412698412</v>
       </c>
       <c r="L23" s="15">
-        <v>-35.897435897435</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="M23" s="15">
-        <v>25</v>
+        <v>30.952380952381</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="F24" s="14">
         <v>102</v>
       </c>
       <c r="G24" s="14">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H24" s="15">
-        <v>27.5</v>
+        <v>10.869565217391</v>
       </c>
       <c r="I24" s="14">
-        <v>277</v>
+        <v>312</v>
       </c>
       <c r="J24" s="14">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="K24" s="15">
-        <v>49.729729729729</v>
+        <v>43.778801843318</v>
       </c>
       <c r="L24" s="15">
-        <v>7.782101167315</v>
+        <v>9.473684210526</v>
       </c>
       <c r="M24" s="15">
-        <v>47.340425531914</v>
+        <v>57.575757575757</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>400</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F25" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>70</v>
+        <v>38.095238095238</v>
       </c>
       <c r="I25" s="14">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J25" s="14">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K25" s="15">
-        <v>110</v>
+        <v>76.470588235294</v>
       </c>
       <c r="L25" s="15">
-        <v>9.090909090909</v>
+        <v>9.756097560975</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D26" s="14">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-30.434782608695</v>
+        <v>140</v>
       </c>
       <c r="F26" s="14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G26" s="14">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H26" s="15">
-        <v>-12.328767123287</v>
+        <v>2.857142857142</v>
       </c>
       <c r="I26" s="14">
+        <v>212</v>
+      </c>
+      <c r="J26" s="14">
         <v>188</v>
       </c>
-      <c r="J26" s="14">
-        <v>178</v>
-      </c>
       <c r="K26" s="15">
-        <v>5.617977528089</v>
+        <v>12.765957446808</v>
       </c>
       <c r="L26" s="15">
-        <v>16.770186335403</v>
+        <v>18.435754189944</v>
       </c>
       <c r="M26" s="15">
-        <v>-23.577235772357</v>
+        <v>-22.909090909090</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>28.571428571428</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>42.857142857142</v>
+        <v>31.25</v>
       </c>
       <c r="L28" s="15">
-        <v>66.666666666666</v>
+        <v>61.538461538461</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
       <c r="J29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L29" s="15">
         <v>-85.714285714285</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.818181818181</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.744680851063</v>
+        <v>-96.551724137931</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
       <c r="J30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-66.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="L30" s="15">
         <v>-84.615384615384</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.555555555555</v>
+        <v>-96.363636363636</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -860,14 +860,14 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="14">
         <v>1</v>
       </c>
       <c r="H14" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -885,48 +885,48 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>4</v>
       </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>42.857142857142</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L15" s="15">
         <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N15" s="15">
-        <v>-56.521739130434</v>
+        <v>-58.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
         <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>81.818181818181</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I16" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J16" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15">
-        <v>42.857142857142</v>
+        <v>34.782608695652</v>
       </c>
       <c r="L16" s="15">
-        <v>-4.761904761904</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M16" s="15">
-        <v>-28.571428571428</v>
+        <v>-35.416666666666</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.304093567251</v>
+        <v>-88.788426763110</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G17" s="14">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H17" s="15">
-        <v>1.785714285714</v>
+        <v>40</v>
       </c>
       <c r="I17" s="14">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="J17" s="14">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.298701298701</v>
+        <v>7.361963190184</v>
       </c>
       <c r="L17" s="15">
-        <v>9.352517985611</v>
+        <v>15.131578947368</v>
       </c>
       <c r="M17" s="15">
-        <v>29.914529914529</v>
+        <v>35.658914728682</v>
       </c>
       <c r="N17" s="15">
-        <v>-27.619047619047</v>
+        <v>-24.892703862660</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>45.454545454545</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>55.172413793103</v>
+        <v>46.875</v>
       </c>
       <c r="L18" s="15">
-        <v>87.5</v>
+        <v>80.769230769230</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.728813559322</v>
+        <v>-29.850746268656</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.431818181818</v>
+        <v>-76.020408163265</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>11</v>
+      </c>
+      <c r="D19" s="14">
         <v>8</v>
       </c>
-      <c r="D19" s="14">
-        <v>16</v>
-      </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>-37.5</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="I19" s="14">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="J19" s="14">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>4.347826086956</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.666666666666</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="M19" s="15">
-        <v>12</v>
+        <v>10.344827586206</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.465753424657</v>
+        <v>-40.372670807453</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.090909090909</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-45.945945945945</v>
+        <v>-41.025641025641</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.076923076923</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.185185185185</v>
+        <v>-84.246575342465</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>6.451612903225</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G21" s="17">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="H21" s="18">
-        <v>1.550387596899</v>
+        <v>25</v>
       </c>
       <c r="I21" s="17">
-        <v>372</v>
+        <v>414</v>
       </c>
       <c r="J21" s="17">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="K21" s="18">
-        <v>9.734513274336</v>
+        <v>12.806539509536</v>
       </c>
       <c r="L21" s="18">
-        <v>2.762430939226</v>
+        <v>5.612244897959</v>
       </c>
       <c r="M21" s="18">
-        <v>-0.534759358288</v>
+        <v>-2.358490566037</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.382716049382</v>
+        <v>-68.778280542986</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-80</v>
+      </c>
+      <c r="I22" s="14">
         <v>3</v>
       </c>
-      <c r="H22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I22" s="14">
-        <v>2</v>
-      </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>-81.818181818181</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="L22" s="15">
-        <v>-90.909090909090</v>
+        <v>-86.956521739130</v>
       </c>
       <c r="M22" s="15">
-        <v>-83.333333333333</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>66.666666666666</v>
+        <v>600</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G23" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-14.285714285714</v>
+        <v>107.142857142857</v>
       </c>
       <c r="I23" s="14">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="J23" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.698412698412</v>
+        <v>6.153846153846</v>
       </c>
       <c r="L23" s="15">
-        <v>-35.294117647058</v>
+        <v>-28.865979381443</v>
       </c>
       <c r="M23" s="15">
-        <v>30.952380952381</v>
+        <v>38</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>6.25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
+        <v>111</v>
+      </c>
+      <c r="G24" s="14">
         <v>102</v>
       </c>
-      <c r="G24" s="14">
-        <v>92</v>
-      </c>
       <c r="H24" s="15">
-        <v>10.869565217391</v>
+        <v>8.823529411764</v>
       </c>
       <c r="I24" s="14">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="J24" s="14">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="K24" s="15">
-        <v>43.778801843318</v>
+        <v>36.437246963562</v>
       </c>
       <c r="L24" s="15">
-        <v>9.473684210526</v>
+        <v>6.645569620253</v>
       </c>
       <c r="M24" s="15">
-        <v>57.575757575757</v>
+        <v>53.881278538812</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
         <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-36.363636363636</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F25" s="14">
+        <v>33</v>
+      </c>
+      <c r="G25" s="14">
         <v>29</v>
       </c>
-      <c r="G25" s="14">
-        <v>21</v>
-      </c>
       <c r="H25" s="15">
-        <v>38.095238095238</v>
+        <v>13.793103448275</v>
       </c>
       <c r="I25" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J25" s="14">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="K25" s="15">
-        <v>76.470588235294</v>
+        <v>61.290322580645</v>
       </c>
       <c r="L25" s="15">
-        <v>9.756097560975</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>140</v>
+        <v>4.761904761904</v>
       </c>
       <c r="F26" s="14">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G26" s="14">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H26" s="15">
-        <v>2.857142857142</v>
+        <v>-1.265822784810</v>
       </c>
       <c r="I26" s="14">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="J26" s="14">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="K26" s="15">
-        <v>12.765957446808</v>
+        <v>11.483253588516</v>
       </c>
       <c r="L26" s="15">
-        <v>18.435754189944</v>
+        <v>17.085427135678</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.909090909090</v>
+        <v>-21.016949152542</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
         <v>25</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
@@ -1444,16 +1444,16 @@
         <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>31.25</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>61.538461538461</v>
+        <v>76.923076923076</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="14">
         <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L29" s="15">
-        <v>-85.714285714285</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="M29" s="15">
-        <v>-85.714285714285</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.551724137931</v>
+        <v>-95.081967213114</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="14">
         <v>7</v>
       </c>
       <c r="K30" s="15">
-        <v>-71.428571428571</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L30" s="15">
-        <v>-84.615384615384</v>
+        <v>-76.923076923076</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.363636363636</v>
+        <v>-94.827586206896</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -885,7 +885,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.307692307692</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
         <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M15" s="15">
         <v>-9.090909090909</v>
       </c>
       <c r="N15" s="15">
-        <v>-58.333333333333</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
+        <v>15</v>
+      </c>
+      <c r="G16" s="14">
         <v>17</v>
       </c>
-      <c r="G16" s="14">
-        <v>11</v>
-      </c>
       <c r="H16" s="15">
-        <v>54.545454545454</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I16" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J16" s="14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="K16" s="15">
-        <v>34.782608695652</v>
+        <v>20</v>
       </c>
       <c r="L16" s="15">
-        <v>-8.823529411764</v>
+        <v>-7.042253521126</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.416666666666</v>
+        <v>-35.922330097087</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.788426763110</v>
+        <v>-89.036544850498</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E17" s="15">
-        <v>133.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="G17" s="14">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="H17" s="15">
-        <v>40</v>
+        <v>40.384615384615</v>
       </c>
       <c r="I17" s="14">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="J17" s="14">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="K17" s="15">
-        <v>7.361963190184</v>
+        <v>6.951871657754</v>
       </c>
       <c r="L17" s="15">
-        <v>15.131578947368</v>
+        <v>22.699386503067</v>
       </c>
       <c r="M17" s="15">
-        <v>35.658914728682</v>
+        <v>39.860139860139</v>
       </c>
       <c r="N17" s="15">
-        <v>-24.892703862660</v>
+        <v>-22.480620155038</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>44.444444444444</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>46.875</v>
+        <v>40</v>
       </c>
       <c r="L18" s="15">
-        <v>80.769230769230</v>
+        <v>53.125</v>
       </c>
       <c r="M18" s="15">
-        <v>-29.850746268656</v>
+        <v>-30</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.020408163265</v>
+        <v>-77.419354838709</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
         <v>11</v>
       </c>
-      <c r="D19" s="14">
-        <v>8</v>
-      </c>
       <c r="E19" s="15">
-        <v>37.5</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.714285714285</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="I19" s="14">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J19" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="K19" s="15">
-        <v>4.347826086956</v>
+        <v>-0.970873786407</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.040816326530</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="M19" s="15">
-        <v>10.344827586206</v>
+        <v>7.368421052631</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.372670807453</v>
+        <v>-44.262295081967</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
         <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>57.142857142857</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>-4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.025641025641</v>
+        <v>-37.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-25.806451612903</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.246575342465</v>
+        <v>-84.076433121019</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E21" s="18">
-        <v>35.714285714285</v>
+        <v>-30.612244897959</v>
       </c>
       <c r="F21" s="17">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G21" s="17">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="H21" s="18">
-        <v>25</v>
+        <v>14.0625</v>
       </c>
       <c r="I21" s="17">
-        <v>414</v>
+        <v>453</v>
       </c>
       <c r="J21" s="17">
-        <v>367</v>
+        <v>416</v>
       </c>
       <c r="K21" s="18">
-        <v>12.806539509536</v>
+        <v>8.894230769230</v>
       </c>
       <c r="L21" s="18">
-        <v>5.612244897959</v>
+        <v>7.600950118764</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.358490566037</v>
+        <v>-1.948051948051</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.778280542986</v>
+        <v>-68.887362637362</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>3</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-80</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>-78.571428571428</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="L22" s="15">
-        <v>-86.956521739130</v>
+        <v>-78.260869565217</v>
       </c>
       <c r="M22" s="15">
-        <v>-78.571428571428</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E23" s="15">
-        <v>600</v>
+        <v>-60</v>
       </c>
       <c r="F23" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H23" s="15">
-        <v>107.142857142857</v>
+        <v>43.478260869565</v>
       </c>
       <c r="I23" s="14">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J23" s="14">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K23" s="15">
-        <v>6.153846153846</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="15">
-        <v>-28.865979381443</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M23" s="15">
-        <v>38</v>
+        <v>43.396226415094</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.666666666666</v>
+        <v>7.407407407407</v>
       </c>
       <c r="F24" s="14">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H24" s="15">
-        <v>8.823529411764</v>
+        <v>-0.917431192660</v>
       </c>
       <c r="I24" s="14">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="J24" s="14">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="K24" s="15">
-        <v>36.437246963562</v>
+        <v>33.211678832116</v>
       </c>
       <c r="L24" s="15">
-        <v>6.645569620253</v>
+        <v>6.725146198830</v>
       </c>
       <c r="M24" s="15">
-        <v>53.881278538812</v>
+        <v>54.008438818565</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>-9.090909090909</v>
+        <v>-12.5</v>
       </c>
       <c r="F25" s="14">
         <v>33</v>
       </c>
       <c r="G25" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H25" s="15">
-        <v>13.793103448275</v>
+        <v>3.125</v>
       </c>
       <c r="I25" s="14">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J25" s="14">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K25" s="15">
-        <v>61.290322580645</v>
+        <v>52.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>11.111111111111</v>
+        <v>13.829787234042</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E26" s="15">
-        <v>4.761904761904</v>
+        <v>113.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G26" s="14">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="H26" s="15">
-        <v>-1.265822784810</v>
+        <v>31.884057971014</v>
       </c>
       <c r="I26" s="14">
-        <v>233</v>
+        <v>262</v>
       </c>
       <c r="J26" s="14">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="K26" s="15">
-        <v>11.483253588516</v>
+        <v>16.964285714285</v>
       </c>
       <c r="L26" s="15">
-        <v>17.085427135678</v>
+        <v>23.584905660377</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.016949152542</v>
+        <v>-17.868338557993</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-80</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="L27" s="15">
         <v>0</v>
-      </c>
-      <c r="L27" s="15">
-        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
         <v>6</v>
-      </c>
-      <c r="G28" s="14">
-        <v>4</v>
       </c>
       <c r="H28" s="15">
         <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>27.777777777777</v>
+        <v>40</v>
       </c>
       <c r="L28" s="15">
-        <v>76.923076923076</v>
+        <v>86.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
@@ -1497,18 +1497,18 @@
         <v>-78.571428571428</v>
       </c>
       <c r="M29" s="15">
-        <v>-78.571428571428</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.081967213114</v>
+        <v>-95.454545454545</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,10 +1520,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
@@ -1538,10 +1538,10 @@
         <v>-76.923076923076</v>
       </c>
       <c r="M30" s="15">
-        <v>-70</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.827586206896</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -879,54 +879,54 @@
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-80</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N14" s="15">
-        <v>-92.857142857142</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L15" s="15">
-        <v>66.666666666666</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M15" s="15">
-        <v>-9.090909090909</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-61.290322580645</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
-        <v>9</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>5</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J16" s="14">
         <v>55</v>
       </c>
       <c r="K16" s="15">
-        <v>20</v>
+        <v>29.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.042253521126</v>
+        <v>-1.388888888888</v>
       </c>
       <c r="M16" s="15">
-        <v>-35.922330097087</v>
+        <v>-36.607142857142</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.036544850498</v>
+        <v>-89.043209876543</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G17" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="15">
-        <v>40.384615384615</v>
+        <v>41.509433962264</v>
       </c>
       <c r="I17" s="14">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="J17" s="14">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K17" s="15">
-        <v>6.951871657754</v>
+        <v>8.629441624365</v>
       </c>
       <c r="L17" s="15">
-        <v>22.699386503067</v>
+        <v>21.590909090909</v>
       </c>
       <c r="M17" s="15">
-        <v>39.860139860139</v>
+        <v>34.591194968553</v>
       </c>
       <c r="N17" s="15">
-        <v>-22.480620155038</v>
+        <v>-22.181818181818</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>40</v>
+        <v>40.540540540540</v>
       </c>
       <c r="L18" s="15">
-        <v>53.125</v>
+        <v>40.540540540540</v>
       </c>
       <c r="M18" s="15">
-        <v>-30</v>
+        <v>-32.467532467532</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.419354838709</v>
+        <v>-77.872340425531</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-36.363636363636</v>
+        <v>-12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.894736842105</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="I19" s="14">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J19" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="K19" s="15">
-        <v>-0.970873786407</v>
+        <v>-1.801801801801</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.923076923076</v>
+        <v>-1.801801801801</v>
       </c>
       <c r="M19" s="15">
-        <v>7.368421052631</v>
+        <v>0.925925925925</v>
       </c>
       <c r="N19" s="15">
-        <v>-44.262295081967</v>
+        <v>-46.568627450980</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
+        <v>6</v>
+      </c>
+      <c r="G20" s="14">
         <v>10</v>
       </c>
-      <c r="G20" s="14">
-        <v>7</v>
-      </c>
       <c r="H20" s="15">
-        <v>42.857142857142</v>
+        <v>-40</v>
       </c>
       <c r="I20" s="14">
         <v>25</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L20" s="15">
+        <v>-40.476190476190</v>
+      </c>
+      <c r="M20" s="15">
         <v>-37.5</v>
       </c>
-      <c r="M20" s="15">
-        <v>-32.432432432432</v>
-      </c>
       <c r="N20" s="15">
-        <v>-84.076433121019</v>
+        <v>-85.380116959064</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D21" s="17">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-30.612244897959</v>
+        <v>28</v>
       </c>
       <c r="F21" s="17">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G21" s="17">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H21" s="18">
-        <v>14.0625</v>
+        <v>6.766917293233</v>
       </c>
       <c r="I21" s="17">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="J21" s="17">
-        <v>416</v>
+        <v>441</v>
       </c>
       <c r="K21" s="18">
-        <v>8.894230769230</v>
+        <v>9.750566893424</v>
       </c>
       <c r="L21" s="18">
-        <v>7.600950118764</v>
+        <v>7.079646017699</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.948051948051</v>
+        <v>-5.283757338551</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.887362637362</v>
+        <v>-69.347688410386</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>-64.285714285714</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L22" s="15">
-        <v>-78.260869565217</v>
+        <v>-73.913043478260</v>
       </c>
       <c r="M22" s="15">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>-60</v>
+        <v>40</v>
       </c>
       <c r="F23" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G23" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H23" s="15">
-        <v>43.478260869565</v>
+        <v>28</v>
       </c>
       <c r="I23" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J23" s="14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K23" s="15">
-        <v>-5</v>
+        <v>-2.352941176470</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.923076923076</v>
+        <v>-26.548672566371</v>
       </c>
       <c r="M23" s="15">
-        <v>43.396226415094</v>
+        <v>38.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>7.407407407407</v>
+        <v>26.086956521739</v>
       </c>
       <c r="F24" s="14">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G24" s="14">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.917431192660</v>
+        <v>2.678571428571</v>
       </c>
       <c r="I24" s="14">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="J24" s="14">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="K24" s="15">
-        <v>33.211678832116</v>
+        <v>31.986531986532</v>
       </c>
       <c r="L24" s="15">
-        <v>6.725146198830</v>
+        <v>10.112359550561</v>
       </c>
       <c r="M24" s="15">
-        <v>54.008438818565</v>
+        <v>53.725490196078</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-12.5</v>
+        <v>75</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G25" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H25" s="15">
-        <v>3.125</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="I25" s="14">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J25" s="14">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K25" s="15">
-        <v>52.857142857142</v>
+        <v>51.351351351351</v>
       </c>
       <c r="L25" s="15">
-        <v>13.829787234042</v>
+        <v>15.463917525773</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" s="15">
-        <v>113.333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="F26" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G26" s="14">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H26" s="15">
-        <v>31.884057971014</v>
+        <v>59.677419354838</v>
       </c>
       <c r="I26" s="14">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="J26" s="14">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="K26" s="15">
-        <v>16.964285714285</v>
+        <v>19.166666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>23.584905660377</v>
+        <v>28.251121076233</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.868338557993</v>
+        <v>-18.980169971671</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-80</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
         <v>0</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>5</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
       <c r="E28" s="15">
-        <v>150</v>
+        <v>-80</v>
       </c>
       <c r="F28" s="14">
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="L28" s="15">
-        <v>86.666666666666</v>
+        <v>61.111111111111</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
         <v>3</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K29" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L29" s="15">
-        <v>-78.571428571428</v>
+        <v>-82.352941176470</v>
       </c>
       <c r="M29" s="15">
-        <v>-83.333333333333</v>
+        <v>-88</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.454545454545</v>
+        <v>-95.945945945946</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L30" s="15">
-        <v>-76.923076923076</v>
+        <v>-80</v>
       </c>
       <c r="M30" s="15">
-        <v>-72.727272727272</v>
+        <v>-82.352941176470</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -879,10 +879,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="M14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="N14" s="15">
         <v>-93.333333333333</v>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>12</v>
@@ -923,10 +923,10 @@
         <v>71.428571428571</v>
       </c>
       <c r="M15" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-61.290322580645</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
-      </c>
-      <c r="D16" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="14">
+        <v>7</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>18</v>
+      </c>
+      <c r="G16" s="14">
         <v>20</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="14">
-        <v>15</v>
-      </c>
-      <c r="G16" s="14">
-        <v>15</v>
-      </c>
       <c r="H16" s="15">
+        <v>-10</v>
+      </c>
+      <c r="I16" s="14">
+        <v>78</v>
+      </c>
+      <c r="J16" s="14">
+        <v>62</v>
+      </c>
+      <c r="K16" s="15">
+        <v>25.806451612903</v>
+      </c>
+      <c r="L16" s="15">
         <v>0</v>
       </c>
-      <c r="I16" s="14">
-        <v>71</v>
-      </c>
-      <c r="J16" s="14">
-        <v>55</v>
-      </c>
-      <c r="K16" s="15">
-        <v>29.090909090909</v>
-      </c>
-      <c r="L16" s="15">
-        <v>-1.388888888888</v>
-      </c>
       <c r="M16" s="15">
-        <v>-36.607142857142</v>
+        <v>-32.758620689655</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.043209876543</v>
+        <v>-88.857142857142</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F17" s="14">
         <v>75</v>
       </c>
       <c r="G17" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H17" s="15">
-        <v>41.509433962264</v>
+        <v>22.950819672131</v>
       </c>
       <c r="I17" s="14">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="J17" s="14">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="K17" s="15">
-        <v>8.629441624365</v>
+        <v>7.441860465116</v>
       </c>
       <c r="L17" s="15">
-        <v>21.590909090909</v>
+        <v>20.942408376963</v>
       </c>
       <c r="M17" s="15">
-        <v>34.591194968553</v>
+        <v>37.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-22.181818181818</v>
+        <v>-22.483221476510</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
         <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="K18" s="15">
-        <v>40.540540540540</v>
+        <v>30.952380952381</v>
       </c>
       <c r="L18" s="15">
-        <v>40.540540540540</v>
+        <v>48.648648648648</v>
       </c>
       <c r="M18" s="15">
-        <v>-32.467532467532</v>
+        <v>-32.098765432098</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.872340425531</v>
+        <v>-78.764478764478</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
+        <v>-23.076923076923</v>
+      </c>
+      <c r="F19" s="14">
+        <v>35</v>
+      </c>
+      <c r="G19" s="14">
+        <v>40</v>
+      </c>
+      <c r="H19" s="15">
         <v>-12.5</v>
       </c>
-      <c r="F19" s="14">
-        <v>33</v>
-      </c>
-      <c r="G19" s="14">
-        <v>43</v>
-      </c>
-      <c r="H19" s="15">
-        <v>-23.255813953488</v>
-      </c>
       <c r="I19" s="14">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J19" s="14">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.801801801801</v>
+        <v>-4.838709677419</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.801801801801</v>
+        <v>0.854700854700</v>
       </c>
       <c r="M19" s="15">
-        <v>0.925925925925</v>
+        <v>2.608695652173</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.568627450980</v>
+        <v>-48.917748917748</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-37.5</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.793103448275</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.476190476190</v>
+        <v>-42.222222222222</v>
       </c>
       <c r="M20" s="15">
-        <v>-37.5</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.380116959064</v>
+        <v>-86.096256684492</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E21" s="18">
-        <v>28</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F21" s="17">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G21" s="17">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="H21" s="18">
-        <v>6.766917293233</v>
+        <v>-0.684931506849</v>
       </c>
       <c r="I21" s="17">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="J21" s="17">
-        <v>441</v>
+        <v>485</v>
       </c>
       <c r="K21" s="18">
-        <v>9.750566893424</v>
+        <v>7.422680412371</v>
       </c>
       <c r="L21" s="18">
-        <v>7.079646017699</v>
+        <v>7.867494824016</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.283757338551</v>
+        <v>-3.696857670979</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.347688410386</v>
+        <v>-69.762042948345</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
@@ -1207,7 +1207,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="L22" s="15">
-        <v>-73.913043478260</v>
+        <v>-76</v>
       </c>
       <c r="M22" s="15">
         <v>-62.5</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
         <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F23" s="14">
         <v>32</v>
       </c>
       <c r="G23" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H23" s="15">
-        <v>28</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I23" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J23" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K23" s="15">
-        <v>-2.352941176470</v>
+        <v>-2.222222222222</v>
       </c>
       <c r="L23" s="15">
-        <v>-26.548672566371</v>
+        <v>-23.478260869565</v>
       </c>
       <c r="M23" s="15">
-        <v>38.333333333333</v>
+        <v>41.935483870967</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>26.086956521739</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F24" s="14">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G24" s="14">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15">
-        <v>2.678571428571</v>
+        <v>3.773584905660</v>
       </c>
       <c r="I24" s="14">
-        <v>392</v>
+        <v>422</v>
       </c>
       <c r="J24" s="14">
-        <v>297</v>
+        <v>323</v>
       </c>
       <c r="K24" s="15">
-        <v>31.986531986532</v>
+        <v>30.650154798761</v>
       </c>
       <c r="L24" s="15">
-        <v>10.112359550561</v>
+        <v>14.986376021798</v>
       </c>
       <c r="M24" s="15">
-        <v>53.725490196078</v>
+        <v>59.245283018867</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="F25" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G25" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H25" s="15">
-        <v>-14.705882352941</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I25" s="14">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J25" s="14">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K25" s="15">
-        <v>51.351351351351</v>
+        <v>48.780487804878</v>
       </c>
       <c r="L25" s="15">
-        <v>15.463917525773</v>
+        <v>24.489795918367</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" s="14">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G26" s="14">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H26" s="15">
-        <v>59.677419354838</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="J26" s="14">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="K26" s="15">
-        <v>19.166666666666</v>
+        <v>17.870722433460</v>
       </c>
       <c r="L26" s="15">
-        <v>28.251121076233</v>
+        <v>26.530612244898</v>
       </c>
       <c r="M26" s="15">
-        <v>-18.980169971671</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,13 +1385,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
@@ -1403,16 +1403,16 @@
         <v>-40</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" s="15">
-        <v>-80</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H28" s="15">
-        <v>-18.181818181818</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J28" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K28" s="15">
-        <v>16</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L28" s="15">
-        <v>61.111111111111</v>
+        <v>78.947368421052</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>2</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
+        <v>3</v>
+      </c>
+      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>8</v>
       </c>
       <c r="K29" s="15">
-        <v>-62.5</v>
+        <v>-37.5</v>
       </c>
       <c r="L29" s="15">
-        <v>-82.352941176470</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="M29" s="15">
-        <v>-88</v>
+        <v>-81.481481481481</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.945945945946</v>
+        <v>-93.975903614457</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2</v>
+      </c>
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="14">
-        <v>1</v>
-      </c>
-      <c r="G30" s="14">
-        <v>2</v>
-      </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>8</v>
       </c>
       <c r="K30" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="M30" s="15">
-        <v>-82.352941176470</v>
+        <v>-78.947368421052</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.714285714285</v>
+        <v>-94.936708860759</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -885,48 +885,48 @@
         <v>-80</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.333333333333</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K15" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
         <v>71.428571428571</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N15" s="15">
-        <v>-63.636363636363</v>
+        <v>-64.705882352941</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H16" s="15">
-        <v>-10</v>
+        <v>-24</v>
       </c>
       <c r="I16" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J16" s="14">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K16" s="15">
-        <v>25.806451612903</v>
+        <v>15.492957746478</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.758620689655</v>
+        <v>-32.786885245901</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.857142857142</v>
+        <v>-89.008042895442</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E17" s="15">
-        <v>-5.555555555555</v>
+        <v>-62.962962962963</v>
       </c>
       <c r="F17" s="14">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="G17" s="14">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="H17" s="15">
-        <v>22.950819672131</v>
+        <v>-22.784810126582</v>
       </c>
       <c r="I17" s="14">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="J17" s="14">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="K17" s="15">
-        <v>7.441860465116</v>
+        <v>-0.413223140495</v>
       </c>
       <c r="L17" s="15">
-        <v>20.942408376963</v>
+        <v>19.900497512437</v>
       </c>
       <c r="M17" s="15">
-        <v>37.5</v>
+        <v>36.931818181818</v>
       </c>
       <c r="N17" s="15">
-        <v>-22.483221476510</v>
+        <v>-24.6875</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-23.076923076923</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="I18" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J18" s="14">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K18" s="15">
-        <v>30.952380952381</v>
+        <v>18.367346938775</v>
       </c>
       <c r="L18" s="15">
-        <v>48.648648648648</v>
+        <v>41.463414634146</v>
       </c>
       <c r="M18" s="15">
-        <v>-32.098765432098</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="N18" s="15">
-        <v>-78.764478764478</v>
+        <v>-79.061371841155</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-23.076923076923</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-12.5</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="I19" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="J19" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.838709677419</v>
+        <v>-5.185185185185</v>
       </c>
       <c r="L19" s="15">
-        <v>0.854700854700</v>
+        <v>2.4</v>
       </c>
       <c r="M19" s="15">
-        <v>2.608695652173</v>
+        <v>0.787401574803</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.917748917748</v>
+        <v>-49.407114624505</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-37.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J20" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.333333333333</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.222222222222</v>
+        <v>-36.956521739130</v>
       </c>
       <c r="M20" s="15">
-        <v>-40.909090909090</v>
+        <v>-39.583333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.096256684492</v>
+        <v>-85.572139303482</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.636363636363</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="F21" s="17">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="G21" s="17">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="H21" s="18">
-        <v>-0.684931506849</v>
+        <v>-25.568181818181</v>
       </c>
       <c r="I21" s="17">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="J21" s="17">
-        <v>485</v>
+        <v>543</v>
       </c>
       <c r="K21" s="18">
-        <v>7.422680412371</v>
+        <v>1.473296500920</v>
       </c>
       <c r="L21" s="18">
-        <v>7.867494824016</v>
+        <v>8.039215686274</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.696857670979</v>
+        <v>-5.163511187607</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.762042948345</v>
+        <v>-70.167839740119</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K22" s="15">
-        <v>-57.142857142857</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="L22" s="15">
-        <v>-76</v>
+        <v>-72</v>
       </c>
       <c r="M22" s="15">
-        <v>-62.5</v>
+        <v>-56.25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
-        <v>20</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F23" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G23" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H23" s="15">
-        <v>18.518518518518</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I23" s="14">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J23" s="14">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="K23" s="15">
-        <v>-2.222222222222</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.478260869565</v>
+        <v>-23.770491803278</v>
       </c>
       <c r="M23" s="15">
-        <v>41.935483870967</v>
+        <v>40.909090909090</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>7.692307692307</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F24" s="14">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="G24" s="14">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="H24" s="15">
-        <v>3.773584905660</v>
+        <v>16.326530612244</v>
       </c>
       <c r="I24" s="14">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="J24" s="14">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="K24" s="15">
-        <v>30.650154798761</v>
+        <v>30.144927536231</v>
       </c>
       <c r="L24" s="15">
-        <v>14.986376021798</v>
+        <v>15.424164524421</v>
       </c>
       <c r="M24" s="15">
-        <v>59.245283018867</v>
+        <v>59.219858156028</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>25</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G25" s="14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H25" s="15">
-        <v>3.225806451612</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I25" s="14">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="J25" s="14">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K25" s="15">
-        <v>48.780487804878</v>
+        <v>47.191011235955</v>
       </c>
       <c r="L25" s="15">
-        <v>24.489795918367</v>
+        <v>25.961538461538</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F26" s="14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G26" s="14">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>15.909090909090</v>
       </c>
       <c r="I26" s="14">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="J26" s="14">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="K26" s="15">
-        <v>17.870722433460</v>
+        <v>11.784511784511</v>
       </c>
       <c r="L26" s="15">
-        <v>26.530612244898</v>
+        <v>29.6875</v>
       </c>
       <c r="M26" s="15">
-        <v>-16.216216216216</v>
+        <v>-17.206982543640</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,19 +1397,19 @@
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L27" s="15">
         <v>8.333333333333</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>-16.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
         <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H28" s="15">
-        <v>-13.333333333333</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I28" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K28" s="15">
-        <v>9.677419354838</v>
+        <v>2.857142857142</v>
       </c>
       <c r="L28" s="15">
-        <v>78.947368421052</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>2</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
+        <v>2</v>
+      </c>
+      <c r="G29" s="14">
         <v>3</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
       <c r="H29" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I29" s="14">
         <v>5</v>
       </c>
       <c r="J29" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K29" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="15">
         <v>-72.222222222222</v>
@@ -1500,39 +1500,39 @@
         <v>-81.481481481481</v>
       </c>
       <c r="N29" s="15">
-        <v>-93.975903614457</v>
+        <v>-94.505494505494</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
       </c>
       <c r="J30" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L30" s="15">
         <v>-75</v>
@@ -1541,7 +1541,7 @@
         <v>-78.947368421052</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.936708860759</v>
+        <v>-95.402298850574</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -879,45 +879,45 @@
         <v>0</v>
       </c>
       <c r="L14" s="15">
-        <v>-87.5</v>
+        <v>-90</v>
       </c>
       <c r="M14" s="15">
         <v>-80</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.75</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>12</v>
       </c>
       <c r="J15" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L15" s="15">
         <v>71.428571428571</v>
@@ -926,7 +926,7 @@
         <v>-7.692307692307</v>
       </c>
       <c r="N15" s="15">
-        <v>-64.705882352941</v>
+        <v>-65.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>-55.555555555555</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H16" s="15">
-        <v>-24</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I16" s="14">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="J16" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K16" s="15">
-        <v>15.492957746478</v>
+        <v>16.883116883116</v>
       </c>
       <c r="L16" s="15">
         <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-32.786885245901</v>
+        <v>-31.297709923664</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.008042895442</v>
+        <v>-88.764044943820</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
         <v>27</v>
       </c>
       <c r="E17" s="15">
-        <v>-62.962962962963</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F17" s="14">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.784810126582</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="I17" s="14">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="J17" s="14">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="K17" s="15">
-        <v>-0.413223140495</v>
+        <v>-5.947955390334</v>
       </c>
       <c r="L17" s="15">
-        <v>19.900497512437</v>
+        <v>16.589861751152</v>
       </c>
       <c r="M17" s="15">
-        <v>36.931818181818</v>
+        <v>38.251366120218</v>
       </c>
       <c r="N17" s="15">
-        <v>-24.6875</v>
+        <v>-25.147928994082</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
+        <v>5</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
         <v>7</v>
       </c>
-      <c r="E18" s="15">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="F18" s="14">
-        <v>8</v>
-      </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-52.941176470588</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="I18" s="14">
         <v>58</v>
       </c>
       <c r="J18" s="14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K18" s="15">
-        <v>18.367346938775</v>
+        <v>7.407407407407</v>
       </c>
       <c r="L18" s="15">
-        <v>41.463414634146</v>
+        <v>20.833333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-35.555555555555</v>
+        <v>-36.956521739130</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.061371841155</v>
+        <v>-80.338983050847</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
         <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-18.181818181818</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
         <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.930232558139</v>
+        <v>-27.906976744186</v>
       </c>
       <c r="I19" s="14">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J19" s="14">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.185185185185</v>
+        <v>-8.904109589041</v>
       </c>
       <c r="L19" s="15">
-        <v>2.4</v>
+        <v>3.100775193798</v>
       </c>
       <c r="M19" s="15">
-        <v>0.787401574803</v>
+        <v>0.757575757575</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.407114624505</v>
+        <v>-52.5</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-22.222222222222</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I20" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J20" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.121212121212</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-36.956521739130</v>
+        <v>-40</v>
       </c>
       <c r="M20" s="15">
-        <v>-39.583333333333</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.572139303482</v>
+        <v>-85.436893203883</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E21" s="18">
-        <v>-48.275862068965</v>
+        <v>-53.703703703703</v>
       </c>
       <c r="F21" s="17">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G21" s="17">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.568181818181</v>
+        <v>-31.491712707182</v>
       </c>
       <c r="I21" s="17">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="J21" s="17">
-        <v>543</v>
+        <v>597</v>
       </c>
       <c r="K21" s="18">
-        <v>1.473296500920</v>
+        <v>-3.350083752093</v>
       </c>
       <c r="L21" s="18">
-        <v>8.039215686274</v>
+        <v>4.718693284936</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.163511187607</v>
+        <v>-5.409836065573</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.167839740119</v>
+        <v>-70.740365111561</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>3</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-44.444444444444</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G23" s="14">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H23" s="15">
-        <v>-32.352941176470</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I23" s="14">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J23" s="14">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.060606060606</v>
+        <v>-4.716981132075</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.770491803278</v>
+        <v>-21.705426356589</v>
       </c>
       <c r="M23" s="15">
-        <v>40.909090909090</v>
+        <v>53.030303030303</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G24" s="14">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H24" s="15">
-        <v>16.326530612244</v>
+        <v>16.842105263157</v>
       </c>
       <c r="I24" s="14">
-        <v>449</v>
+        <v>475</v>
       </c>
       <c r="J24" s="14">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="K24" s="15">
-        <v>30.144927536231</v>
+        <v>28.726287262872</v>
       </c>
       <c r="L24" s="15">
-        <v>15.424164524421</v>
+        <v>15.012106537530</v>
       </c>
       <c r="M24" s="15">
-        <v>59.219858156028</v>
+        <v>62.116040955631</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>28.571428571428</v>
+        <v>75</v>
       </c>
       <c r="F25" s="14">
         <v>33</v>
       </c>
       <c r="G25" s="14">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H25" s="15">
-        <v>22.222222222222</v>
+        <v>43.478260869565</v>
       </c>
       <c r="I25" s="14">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J25" s="14">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K25" s="15">
-        <v>47.191011235955</v>
+        <v>48.387096774193</v>
       </c>
       <c r="L25" s="15">
-        <v>25.961538461538</v>
+        <v>26.605504587156</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D26" s="14">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15">
-        <v>-35.294117647058</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="G26" s="14">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H26" s="15">
-        <v>15.909090909090</v>
+        <v>-15</v>
       </c>
       <c r="I26" s="14">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="J26" s="14">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="K26" s="15">
-        <v>11.784511784511</v>
+        <v>6.790123456790</v>
       </c>
       <c r="L26" s="15">
-        <v>29.6875</v>
+        <v>28.148148148148</v>
       </c>
       <c r="M26" s="15">
-        <v>-17.206982543640</v>
+        <v>-20.092378752886</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>-7.142857142857</v>
+        <v>-18.75</v>
       </c>
       <c r="L27" s="15">
         <v>8.333333333333</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H28" s="15">
-        <v>-23.529411764705</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
+        <v>39</v>
+      </c>
+      <c r="J28" s="14">
         <v>36</v>
       </c>
-      <c r="J28" s="14">
-        <v>35</v>
-      </c>
       <c r="K28" s="15">
-        <v>2.857142857142</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>71.428571428571</v>
+        <v>85.714285714285</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>2</v>
       </c>
       <c r="D29" s="14">
         <v>2</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I29" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>-72.222222222222</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.481481481481</v>
+        <v>-74.074074074074</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.505494505494</v>
+        <v>-92.631578947368</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I30" s="14">
+        <v>5</v>
+      </c>
+      <c r="J30" s="14">
+        <v>10</v>
+      </c>
+      <c r="K30" s="15">
         <v>-50</v>
       </c>
-      <c r="I30" s="14">
-        <v>4</v>
-      </c>
-      <c r="J30" s="14">
-        <v>9</v>
-      </c>
-      <c r="K30" s="15">
-        <v>-55.555555555555</v>
-      </c>
       <c r="L30" s="15">
-        <v>-75</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="M30" s="15">
-        <v>-78.947368421052</v>
+        <v>-73.684210526315</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.402298850574</v>
+        <v>-94.505494505494</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-073pct.xlsx
+++ b/data/source/weekly/cs-en-us-073pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,63 +870,63 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>1</v>
       </c>
       <c r="K14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14" s="15">
-        <v>-90</v>
+        <v>-80</v>
       </c>
       <c r="M14" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-94.117647058823</v>
+        <v>-89.473684210526</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
         <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>71.428571428571</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M15" s="15">
-        <v>-7.692307692307</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N15" s="15">
-        <v>-65.714285714285</v>
+        <v>-63.157894736842</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>16.666666666666</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F16" s="14">
         <v>24</v>
       </c>
       <c r="G16" s="14">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="H16" s="15">
-        <v>9.090909090909</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J16" s="14">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K16" s="15">
-        <v>16.883116883116</v>
+        <v>7.954545454545</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>2.150537634408</v>
       </c>
       <c r="M16" s="15">
-        <v>-31.297709923664</v>
+        <v>-33.098591549295</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.764044943820</v>
+        <v>-88.730723606168</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,54 +975,54 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" s="14">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>-55.555555555555</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F17" s="14">
         <v>54</v>
       </c>
       <c r="G17" s="14">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H17" s="15">
-        <v>-34.146341463414</v>
+        <v>-39.325842696629</v>
       </c>
       <c r="I17" s="14">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="J17" s="14">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.947955390334</v>
+        <v>-5.244755244755</v>
       </c>
       <c r="L17" s="15">
-        <v>16.589861751152</v>
+        <v>14.830508474576</v>
       </c>
       <c r="M17" s="15">
-        <v>38.251366120218</v>
+        <v>38.265306122449</v>
       </c>
       <c r="N17" s="15">
-        <v>-25.147928994082</v>
+        <v>-27.345844504021</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>7</v>
@@ -1034,22 +1034,22 @@
         <v>-63.157894736842</v>
       </c>
       <c r="I18" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J18" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>7.407407407407</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L18" s="15">
-        <v>20.833333333333</v>
+        <v>22.448979591836</v>
       </c>
       <c r="M18" s="15">
-        <v>-36.956521739130</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N18" s="15">
-        <v>-80.338983050847</v>
+        <v>-80.582524271844</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-54.545454545454</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
         <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H19" s="15">
-        <v>-27.906976744186</v>
+        <v>-34.042553191489</v>
       </c>
       <c r="I19" s="14">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="J19" s="14">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.904109589041</v>
+        <v>-10.759493670886</v>
       </c>
       <c r="L19" s="15">
-        <v>3.100775193798</v>
+        <v>4.444444444444</v>
       </c>
       <c r="M19" s="15">
-        <v>0.757575757575</v>
+        <v>2.173913043478</v>
       </c>
       <c r="N19" s="15">
-        <v>-52.5</v>
+        <v>-52.525252525252</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-45.454545454545</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L20" s="15">
-        <v>-40</v>
+        <v>-39.622641509434</v>
       </c>
       <c r="M20" s="15">
-        <v>-44.444444444444</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.436893203883</v>
+        <v>-84.976525821596</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E21" s="18">
-        <v>-53.703703703703</v>
+        <v>-29.545454545454</v>
       </c>
       <c r="F21" s="17">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G21" s="17">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="H21" s="18">
-        <v>-31.491712707182</v>
+        <v>-36.5</v>
       </c>
       <c r="I21" s="17">
-        <v>577</v>
+        <v>615</v>
       </c>
       <c r="J21" s="17">
-        <v>597</v>
+        <v>641</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.350083752093</v>
+        <v>-4.056162246489</v>
       </c>
       <c r="L21" s="18">
-        <v>4.718693284936</v>
+        <v>5.128205128205</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.409836065573</v>
+        <v>-6.106870229007</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.740365111561</v>
+        <v>-70.602294455066</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,32 +1182,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>-58.823529411764</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="L22" s="15">
-        <v>-72</v>
+        <v>-73.076923076923</v>
       </c>
       <c r="M22" s="15">
         <v>-56.25</v>
@@ -1224,34 +1224,34 @@
         <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="F23" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G23" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H23" s="15">
-        <v>-3.846153846153</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I23" s="14">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J23" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K23" s="15">
-        <v>-4.716981132075</v>
+        <v>-4.385964912280</v>
       </c>
       <c r="L23" s="15">
-        <v>-21.705426356589</v>
+        <v>-18.045112781954</v>
       </c>
       <c r="M23" s="15">
-        <v>53.030303030303</v>
+        <v>45.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>8.333333333333</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="F24" s="14">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G24" s="14">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15">
-        <v>16.842105263157</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>475</v>
+        <v>500</v>
       </c>
       <c r="J24" s="14">
-        <v>369</v>
+        <v>402</v>
       </c>
       <c r="K24" s="15">
-        <v>28.726287262872</v>
+        <v>24.378109452736</v>
       </c>
       <c r="L24" s="15">
-        <v>15.012106537530</v>
+        <v>15.740740740740</v>
       </c>
       <c r="M24" s="15">
-        <v>62.116040955631</v>
+        <v>60.771704180064</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E25" s="15">
-        <v>75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G25" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H25" s="15">
-        <v>43.478260869565</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I25" s="14">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="J25" s="14">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="K25" s="15">
-        <v>48.387096774193</v>
+        <v>41.176470588235</v>
       </c>
       <c r="L25" s="15">
-        <v>26.605504587156</v>
+        <v>27.433628318584</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D26" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G26" s="14">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H26" s="15">
-        <v>-15</v>
+        <v>-22.321428571428</v>
       </c>
       <c r="I26" s="14">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="J26" s="14">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="K26" s="15">
-        <v>6.790123456790</v>
+        <v>5.397727272727</v>
       </c>
       <c r="L26" s="15">
-        <v>28.148148148148</v>
+        <v>28.819444444444</v>
       </c>
       <c r="M26" s="15">
-        <v>-20.092378752886</v>
+        <v>-20.726495726495</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
@@ -1403,16 +1403,16 @@
         <v>-40</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-18.75</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L27" s="15">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>300</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I28" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J28" s="14">
         <v>36</v>
       </c>
       <c r="K28" s="15">
-        <v>8.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>85.714285714285</v>
+        <v>90.909090909090</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,40 +1467,40 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
-      </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
+        <v>5</v>
+      </c>
+      <c r="G29" s="14">
         <v>4</v>
       </c>
-      <c r="G29" s="14">
-        <v>5</v>
-      </c>
       <c r="H29" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="I29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="14">
         <v>12</v>
       </c>
       <c r="K29" s="15">
-        <v>-41.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L29" s="15">
-        <v>-66.666666666666</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="M29" s="15">
-        <v>-74.074074074074</v>
+        <v>-72.413793103448</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.631578947368</v>
+        <v>-92.380952380952</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
+        <v>3</v>
+      </c>
+      <c r="G30" s="14">
         <v>2</v>
       </c>
-      <c r="G30" s="14">
-        <v>3</v>
-      </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="14">
         <v>10</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="L30" s="15">
-        <v>-72.222222222222</v>
+        <v>-70</v>
       </c>
       <c r="M30" s="15">
-        <v>-73.684210526315</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.505494505494</v>
+        <v>-94</v>
       </c>
     </row>
     <row r="31" spans="1:14">
